--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29436,7 +29436,7 @@
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>45940.6450231481</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B1089" t="n">
         <v>2600</v>
@@ -29457,6 +29457,32 @@
         <v>43</v>
       </c>
       <c r="H1089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>45943.644849537</v>
+      </c>
+      <c r="B1090" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29462,7 +29462,7 @@
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>45943.644849537</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1090" t="n">
         <v>800</v>
@@ -29483,6 +29483,32 @@
         <v>43</v>
       </c>
       <c r="H1090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>45944.6447222222</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29488,7 +29488,7 @@
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>45944.6447222222</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B1091" t="n">
         <v>1800</v>
@@ -29509,6 +29509,32 @@
         <v>138</v>
       </c>
       <c r="H1091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>45945.6441435185</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29514,7 +29514,7 @@
     </row>
     <row r="1092">
       <c r="A1092" s="1" t="n">
-        <v>45945.6441435185</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1092" t="n">
         <v>2800</v>
@@ -29535,6 +29535,32 @@
         <v>138</v>
       </c>
       <c r="H1092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>45946.4593287037</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>9600</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29540,7 +29540,7 @@
     </row>
     <row r="1093">
       <c r="A1093" s="1" t="n">
-        <v>45946.4593287037</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1093" t="n">
         <v>9600</v>
@@ -29561,6 +29561,32 @@
         <v>138</v>
       </c>
       <c r="H1093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>45947.5943634259</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29566,7 +29566,7 @@
     </row>
     <row r="1094">
       <c r="A1094" s="1" t="n">
-        <v>45947.5943634259</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B1094" t="n">
         <v>1000</v>
@@ -29587,6 +29587,32 @@
         <v>138</v>
       </c>
       <c r="H1094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>45950.6440740741</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29592,7 +29592,7 @@
     </row>
     <row r="1095">
       <c r="A1095" s="1" t="n">
-        <v>45950.6440740741</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B1095" t="n">
         <v>7800</v>
@@ -29613,6 +29613,32 @@
         <v>138</v>
       </c>
       <c r="H1095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>45951.5204282407</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>16600</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29618,7 +29618,7 @@
     </row>
     <row r="1096">
       <c r="A1096" s="1" t="n">
-        <v>45951.5204282407</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1096" t="n">
         <v>16600</v>
@@ -29639,6 +29639,32 @@
         <v>138</v>
       </c>
       <c r="H1096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="1" t="n">
+        <v>45952.5761226852</v>
+      </c>
+      <c r="B1097" t="n">
+        <v>14200</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1097" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29644,7 +29644,7 @@
     </row>
     <row r="1097">
       <c r="A1097" s="1" t="n">
-        <v>45952.5761226852</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B1097" t="n">
         <v>14200</v>
@@ -29665,6 +29665,32 @@
         <v>44</v>
       </c>
       <c r="H1097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="1" t="n">
+        <v>45953.60875</v>
+      </c>
+      <c r="B1098" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1098" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29670,7 +29670,7 @@
     </row>
     <row r="1098">
       <c r="A1098" s="1" t="n">
-        <v>45953.60875</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1098" t="n">
         <v>91200</v>
@@ -29691,6 +29691,32 @@
         <v>139</v>
       </c>
       <c r="H1098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>45954.6385763889</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>112600</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29696,7 +29696,7 @@
     </row>
     <row r="1099">
       <c r="A1099" s="1" t="n">
-        <v>45954.6385763889</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B1099" t="n">
         <v>112600</v>
@@ -29717,6 +29717,32 @@
         <v>139</v>
       </c>
       <c r="H1099" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>45957.6797337963</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>35400</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1100" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29722,7 +29722,7 @@
     </row>
     <row r="1100">
       <c r="A1100" s="1" t="n">
-        <v>45957.6797337963</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1100" t="n">
         <v>35400</v>
@@ -29743,6 +29743,32 @@
         <v>139</v>
       </c>
       <c r="H1100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="1" t="n">
+        <v>45958.6865972222</v>
+      </c>
+      <c r="B1101" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29748,7 +29748,7 @@
     </row>
     <row r="1101">
       <c r="A1101" s="1" t="n">
-        <v>45958.6865972222</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B1101" t="n">
         <v>25400</v>
@@ -29769,6 +29769,32 @@
         <v>139</v>
       </c>
       <c r="H1101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="1" t="n">
+        <v>45959.629849537</v>
+      </c>
+      <c r="B1102" t="n">
+        <v>8200</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1102" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29774,7 +29774,7 @@
     </row>
     <row r="1102">
       <c r="A1102" s="1" t="n">
-        <v>45959.629849537</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1102" t="n">
         <v>8200</v>
@@ -29795,6 +29795,32 @@
         <v>139</v>
       </c>
       <c r="H1102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="1" t="n">
+        <v>45960.6625347222</v>
+      </c>
+      <c r="B1103" t="n">
+        <v>19400</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -811,6 +811,9 @@
   <si>
     <t xml:space="preserve">12.6999998092651</t>
   </si>
+  <si>
+    <t xml:space="preserve">12.8999996185303</t>
+  </si>
 </sst>
 </file>
 
@@ -29800,7 +29803,7 @@
     </row>
     <row r="1103">
       <c r="A1103" s="1" t="n">
-        <v>45960.6625347222</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B1103" t="n">
         <v>19400</v>
@@ -29821,6 +29824,32 @@
         <v>139</v>
       </c>
       <c r="H1103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="1" t="n">
+        <v>45961.6801041667</v>
+      </c>
+      <c r="B1104" t="n">
+        <v>24400</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29829,7 +29829,7 @@
     </row>
     <row r="1104">
       <c r="A1104" s="1" t="n">
-        <v>45961.6801041667</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B1104" t="n">
         <v>24400</v>
@@ -29850,6 +29850,32 @@
         <v>266</v>
       </c>
       <c r="H1104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="1" t="n">
+        <v>45964.6910416667</v>
+      </c>
+      <c r="B1105" t="n">
+        <v>13400</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1105" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29855,7 +29855,7 @@
     </row>
     <row r="1105">
       <c r="A1105" s="1" t="n">
-        <v>45964.6910416667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1105" t="n">
         <v>13400</v>
@@ -29876,6 +29876,32 @@
         <v>266</v>
       </c>
       <c r="H1105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="1" t="n">
+        <v>45965.6475925926</v>
+      </c>
+      <c r="B1106" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29881,7 +29881,7 @@
     </row>
     <row r="1106">
       <c r="A1106" s="1" t="n">
-        <v>45965.6475925926</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B1106" t="n">
         <v>600</v>
@@ -29902,6 +29902,32 @@
         <v>266</v>
       </c>
       <c r="H1106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>45966.6690856481</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>11800</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29907,10 +29907,10 @@
     </row>
     <row r="1107">
       <c r="A1107" s="1" t="n">
-        <v>45966.6690856481</v>
+        <v>45967.6831134259</v>
       </c>
       <c r="B1107" t="n">
-        <v>11800</v>
+        <v>34600</v>
       </c>
       <c r="C1107" t="n">
         <v>12.9499998092651</v>
@@ -29922,10 +29922,10 @@
         <v>12.8999996185303</v>
       </c>
       <c r="F1107" t="n">
-        <v>12.8999996185303</v>
+        <v>12.9499998092651</v>
       </c>
       <c r="G1107" t="s">
-        <v>266</v>
+        <v>139</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29905,32 +29905,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1107">
-      <c r="A1107" s="1" t="n">
-        <v>45967.6831134259</v>
-      </c>
-      <c r="B1107" t="n">
-        <v>34600</v>
-      </c>
-      <c r="C1107" t="n">
-        <v>12.9499998092651</v>
-      </c>
-      <c r="D1107" t="n">
-        <v>12.8999996185303</v>
-      </c>
-      <c r="E1107" t="n">
-        <v>12.8999996185303</v>
-      </c>
-      <c r="F1107" t="n">
-        <v>12.9499998092651</v>
-      </c>
-      <c r="G1107" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1107" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29905,6 +29905,84 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1107">
+      <c r="A1107" s="1" t="n">
+        <v>45966.3333333333</v>
+      </c>
+      <c r="B1107" t="n">
+        <v>11800</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1108" t="n">
+        <v>34600</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -29983,6 +29983,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" s="1" t="n">
+        <v>45971.3333333333</v>
+      </c>
+      <c r="B1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="1" t="n">
+        <v>45972.4599652778</v>
+      </c>
+      <c r="B1111" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30011,7 +30011,7 @@
     </row>
     <row r="1111">
       <c r="A1111" s="1" t="n">
-        <v>45972.4599652778</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B1111" t="n">
         <v>400</v>
@@ -30032,6 +30032,32 @@
         <v>139</v>
       </c>
       <c r="H1111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="1" t="n">
+        <v>45973.564849537</v>
+      </c>
+      <c r="B1112" t="n">
+        <v>25600</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1112" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30037,7 +30037,7 @@
     </row>
     <row r="1112">
       <c r="A1112" s="1" t="n">
-        <v>45973.564849537</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B1112" t="n">
         <v>25600</v>
@@ -30058,6 +30058,32 @@
         <v>139</v>
       </c>
       <c r="H1112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="1" t="n">
+        <v>45974.6128935185</v>
+      </c>
+      <c r="B1113" t="n">
+        <v>12400</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1113" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30063,7 +30063,7 @@
     </row>
     <row r="1113">
       <c r="A1113" s="1" t="n">
-        <v>45974.6128935185</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B1113" t="n">
         <v>12400</v>
@@ -30084,6 +30084,32 @@
         <v>266</v>
       </c>
       <c r="H1113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="1" t="n">
+        <v>45975.6821643518</v>
+      </c>
+      <c r="B1114" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1114" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30089,7 +30089,7 @@
     </row>
     <row r="1114">
       <c r="A1114" s="1" t="n">
-        <v>45975.6821643518</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1114" t="n">
         <v>400</v>
@@ -30110,6 +30110,32 @@
         <v>266</v>
       </c>
       <c r="H1114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="1" t="n">
+        <v>45978.6535069444</v>
+      </c>
+      <c r="B1115" t="n">
+        <v>8200</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1115" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30115,7 +30115,7 @@
     </row>
     <row r="1115">
       <c r="A1115" s="1" t="n">
-        <v>45978.6535069444</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B1115" t="n">
         <v>8200</v>
@@ -30136,6 +30136,32 @@
         <v>266</v>
       </c>
       <c r="H1115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="1" t="n">
+        <v>45979.5021064815</v>
+      </c>
+      <c r="B1116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1116" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30141,7 +30141,7 @@
     </row>
     <row r="1116">
       <c r="A1116" s="1" t="n">
-        <v>45979.5021064815</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B1116" t="n">
         <v>2000</v>
@@ -30162,6 +30162,32 @@
         <v>266</v>
       </c>
       <c r="H1116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="1" t="n">
+        <v>45980.4732060185</v>
+      </c>
+      <c r="B1117" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1117" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1117" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30167,7 +30167,7 @@
     </row>
     <row r="1117">
       <c r="A1117" s="1" t="n">
-        <v>45980.4732060185</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1117" t="n">
         <v>4800</v>
@@ -30188,6 +30188,32 @@
         <v>266</v>
       </c>
       <c r="H1117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="1" t="n">
+        <v>45981.6318981481</v>
+      </c>
+      <c r="B1118" t="n">
+        <v>14400</v>
+      </c>
+      <c r="C1118" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1118" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30193,7 +30193,7 @@
     </row>
     <row r="1118">
       <c r="A1118" s="1" t="n">
-        <v>45981.6318981481</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B1118" t="n">
         <v>14400</v>
@@ -30214,6 +30214,32 @@
         <v>139</v>
       </c>
       <c r="H1118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="1" t="n">
+        <v>45982.5148611111</v>
+      </c>
+      <c r="B1119" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1119" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1119" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30219,7 +30219,7 @@
     </row>
     <row r="1119">
       <c r="A1119" s="1" t="n">
-        <v>45982.5148611111</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B1119" t="n">
         <v>4800</v>
@@ -30240,6 +30240,32 @@
         <v>266</v>
       </c>
       <c r="H1119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="1" t="n">
+        <v>45985.354212963</v>
+      </c>
+      <c r="B1120" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1120" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1120" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30245,7 +30245,7 @@
     </row>
     <row r="1120">
       <c r="A1120" s="1" t="n">
-        <v>45985.354212963</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B1120" t="n">
         <v>200</v>
@@ -30266,6 +30266,32 @@
         <v>266</v>
       </c>
       <c r="H1120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="1" t="n">
+        <v>45986.6204050926</v>
+      </c>
+      <c r="B1121" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1121" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30271,7 +30271,7 @@
     </row>
     <row r="1121">
       <c r="A1121" s="1" t="n">
-        <v>45986.6204050926</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1121" t="n">
         <v>600</v>
@@ -30292,6 +30292,32 @@
         <v>266</v>
       </c>
       <c r="H1121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="1" t="n">
+        <v>45987.3697453704</v>
+      </c>
+      <c r="B1122" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1122" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30297,7 +30297,7 @@
     </row>
     <row r="1122">
       <c r="A1122" s="1" t="n">
-        <v>45987.3697453704</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B1122" t="n">
         <v>200</v>
@@ -30318,6 +30318,32 @@
         <v>266</v>
       </c>
       <c r="H1122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="1" t="n">
+        <v>45988.5728009259</v>
+      </c>
+      <c r="B1123" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1123" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30323,7 +30323,7 @@
     </row>
     <row r="1123">
       <c r="A1123" s="1" t="n">
-        <v>45988.5728009259</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B1123" t="n">
         <v>4800</v>
@@ -30344,6 +30344,32 @@
         <v>266</v>
       </c>
       <c r="H1123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="1" t="n">
+        <v>45989.5402083333</v>
+      </c>
+      <c r="B1124" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1124" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1124" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30349,7 +30349,7 @@
     </row>
     <row r="1124">
       <c r="A1124" s="1" t="n">
-        <v>45989.5402083333</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B1124" t="n">
         <v>1200</v>
@@ -30370,6 +30370,32 @@
         <v>266</v>
       </c>
       <c r="H1124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="1" t="n">
+        <v>45992.6055671296</v>
+      </c>
+      <c r="B1125" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1125" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30375,7 +30375,7 @@
     </row>
     <row r="1125">
       <c r="A1125" s="1" t="n">
-        <v>45992.6055671296</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B1125" t="n">
         <v>3600</v>
@@ -30396,6 +30396,32 @@
         <v>266</v>
       </c>
       <c r="H1125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="1" t="n">
+        <v>45993.6691898148</v>
+      </c>
+      <c r="B1126" t="n">
+        <v>98000</v>
+      </c>
+      <c r="C1126" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1126" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30401,7 +30401,7 @@
     </row>
     <row r="1126">
       <c r="A1126" s="1" t="n">
-        <v>45993.6691898148</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B1126" t="n">
         <v>98000</v>
@@ -30422,6 +30422,32 @@
         <v>266</v>
       </c>
       <c r="H1126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="1" t="n">
+        <v>45994.4151736111</v>
+      </c>
+      <c r="B1127" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1127" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1127" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30427,7 +30427,7 @@
     </row>
     <row r="1127">
       <c r="A1127" s="1" t="n">
-        <v>45994.4151736111</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B1127" t="n">
         <v>4800</v>
@@ -30448,6 +30448,32 @@
         <v>139</v>
       </c>
       <c r="H1127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="1" t="n">
+        <v>45995.5721990741</v>
+      </c>
+      <c r="B1128" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1128" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30453,7 +30453,7 @@
     </row>
     <row r="1128">
       <c r="A1128" s="1" t="n">
-        <v>45995.5721990741</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B1128" t="n">
         <v>6000</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30477,6 +30477,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1129">
+      <c r="A1129" s="1" t="n">
+        <v>45996.3333333333</v>
+      </c>
+      <c r="B1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30503,6 +30503,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1130">
+      <c r="A1130" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1130" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1130" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30529,6 +30529,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1131">
+      <c r="A1131" s="1" t="n">
+        <v>46000.3333333333</v>
+      </c>
+      <c r="B1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30555,6 +30555,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1132">
+      <c r="A1132" s="1" t="n">
+        <v>46001.3333333333</v>
+      </c>
+      <c r="B1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30581,6 +30581,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1133">
+      <c r="A1133" s="1" t="n">
+        <v>46002.3333333333</v>
+      </c>
+      <c r="B1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1133" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="1" t="n">
+        <v>46003.6096759259</v>
+      </c>
+      <c r="B1134" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1134" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30609,7 +30609,7 @@
     </row>
     <row r="1134">
       <c r="A1134" s="1" t="n">
-        <v>46003.6096759259</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B1134" t="n">
         <v>5000</v>
@@ -30630,6 +30630,32 @@
         <v>139</v>
       </c>
       <c r="H1134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="1" t="n">
+        <v>46006.6912847222</v>
+      </c>
+      <c r="B1135" t="n">
+        <v>281600</v>
+      </c>
+      <c r="C1135" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1135" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1135" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30635,7 +30635,7 @@
     </row>
     <row r="1135">
       <c r="A1135" s="1" t="n">
-        <v>46006.6912847222</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B1135" t="n">
         <v>281600</v>
@@ -30656,6 +30656,32 @@
         <v>139</v>
       </c>
       <c r="H1135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="1" t="n">
+        <v>46007.6846875</v>
+      </c>
+      <c r="B1136" t="n">
+        <v>119400</v>
+      </c>
+      <c r="C1136" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1136" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30661,7 +30661,7 @@
     </row>
     <row r="1136">
       <c r="A1136" s="1" t="n">
-        <v>46007.6846875</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B1136" t="n">
         <v>119400</v>
@@ -30682,6 +30682,32 @@
         <v>59</v>
       </c>
       <c r="H1136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="1" t="n">
+        <v>46008.6829398148</v>
+      </c>
+      <c r="B1137" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1137" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1137" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30687,7 +30687,7 @@
     </row>
     <row r="1137">
       <c r="A1137" s="1" t="n">
-        <v>46008.6829398148</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B1137" t="n">
         <v>200000</v>
@@ -30708,6 +30708,32 @@
         <v>59</v>
       </c>
       <c r="H1137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="1" t="n">
+        <v>46009.682974537</v>
+      </c>
+      <c r="B1138" t="n">
+        <v>56400</v>
+      </c>
+      <c r="C1138" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1138" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1138" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30713,7 +30713,7 @@
     </row>
     <row r="1138">
       <c r="A1138" s="1" t="n">
-        <v>46009.682974537</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B1138" t="n">
         <v>56400</v>
@@ -30734,6 +30734,32 @@
         <v>59</v>
       </c>
       <c r="H1138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="1" t="n">
+        <v>46010.6935416667</v>
+      </c>
+      <c r="B1139" t="n">
+        <v>39400</v>
+      </c>
+      <c r="C1139" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1139" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1139" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30739,7 +30739,7 @@
     </row>
     <row r="1139">
       <c r="A1139" s="1" t="n">
-        <v>46010.6935416667</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B1139" t="n">
         <v>39400</v>
@@ -30760,6 +30760,32 @@
         <v>59</v>
       </c>
       <c r="H1139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="1" t="n">
+        <v>46013.6858796296</v>
+      </c>
+      <c r="B1140" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1140" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1140" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1140" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30765,7 +30765,7 @@
     </row>
     <row r="1140">
       <c r="A1140" s="1" t="n">
-        <v>46013.6858796296</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B1140" t="n">
         <v>12000</v>
@@ -30786,6 +30786,32 @@
         <v>59</v>
       </c>
       <c r="H1140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="1" t="n">
+        <v>46014.6911689815</v>
+      </c>
+      <c r="B1141" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C1141" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1141" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1141" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30791,7 +30791,7 @@
     </row>
     <row r="1141">
       <c r="A1141" s="1" t="n">
-        <v>46014.6911689815</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B1141" t="n">
         <v>13800</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30815,6 +30815,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1142">
+      <c r="A1142" s="1" t="n">
+        <v>46020.6364930556</v>
+      </c>
+      <c r="B1142" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1142" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30817,7 +30817,7 @@
     </row>
     <row r="1142">
       <c r="A1142" s="1" t="n">
-        <v>46020.6364930556</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B1142" t="n">
         <v>1600</v>
@@ -30838,6 +30838,32 @@
         <v>139</v>
       </c>
       <c r="H1142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="1" t="n">
+        <v>46021.3796412037</v>
+      </c>
+      <c r="B1143" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1143" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1143" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1143" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30843,7 +30843,7 @@
     </row>
     <row r="1143">
       <c r="A1143" s="1" t="n">
-        <v>46021.3796412037</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B1143" t="n">
         <v>200</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30867,6 +30867,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1144">
+      <c r="A1144" s="1" t="n">
+        <v>46024.4936342593</v>
+      </c>
+      <c r="B1144" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1144" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1144" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30869,7 +30869,7 @@
     </row>
     <row r="1144">
       <c r="A1144" s="1" t="n">
-        <v>46024.4936342593</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B1144" t="n">
         <v>600</v>
@@ -30890,6 +30890,32 @@
         <v>139</v>
       </c>
       <c r="H1144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="1" t="n">
+        <v>46027.6796296296</v>
+      </c>
+      <c r="B1145" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1145" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1145" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1145" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30895,7 +30895,7 @@
     </row>
     <row r="1145">
       <c r="A1145" s="1" t="n">
-        <v>46027.6796296296</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B1145" t="n">
         <v>20000</v>
@@ -30916,6 +30916,32 @@
         <v>59</v>
       </c>
       <c r="H1145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="1" t="n">
+        <v>46028.3624884259</v>
+      </c>
+      <c r="B1146" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1146" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1146" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1146" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30921,7 +30921,7 @@
     </row>
     <row r="1146">
       <c r="A1146" s="1" t="n">
-        <v>46028.3624884259</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B1146" t="n">
         <v>200</v>
@@ -30942,6 +30942,32 @@
         <v>139</v>
       </c>
       <c r="H1146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="1" t="n">
+        <v>46029.654837963</v>
+      </c>
+      <c r="B1147" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1147" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1147" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1147" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30947,7 +30947,7 @@
     </row>
     <row r="1147">
       <c r="A1147" s="1" t="n">
-        <v>46029.654837963</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B1147" t="n">
         <v>400</v>
@@ -30968,6 +30968,32 @@
         <v>139</v>
       </c>
       <c r="H1147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="1" t="n">
+        <v>46030.4598148148</v>
+      </c>
+      <c r="B1148" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C1148" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1148" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1148" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30973,7 +30973,7 @@
     </row>
     <row r="1148">
       <c r="A1148" s="1" t="n">
-        <v>46030.4598148148</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B1148" t="n">
         <v>6600</v>
@@ -30994,6 +30994,32 @@
         <v>139</v>
       </c>
       <c r="H1148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="1" t="n">
+        <v>46031.505162037</v>
+      </c>
+      <c r="B1149" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1149" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1149" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -30999,7 +30999,7 @@
     </row>
     <row r="1149">
       <c r="A1149" s="1" t="n">
-        <v>46031.505162037</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B1149" t="n">
         <v>200</v>
@@ -31020,6 +31020,32 @@
         <v>139</v>
       </c>
       <c r="H1149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="1" t="n">
+        <v>46034.4409259259</v>
+      </c>
+      <c r="B1150" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1150" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1150" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31025,7 +31025,7 @@
     </row>
     <row r="1150">
       <c r="A1150" s="1" t="n">
-        <v>46034.4409259259</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B1150" t="n">
         <v>1600</v>
@@ -31046,6 +31046,32 @@
         <v>139</v>
       </c>
       <c r="H1150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="1" t="n">
+        <v>46035.4374768518</v>
+      </c>
+      <c r="B1151" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1151" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31051,7 +31051,7 @@
     </row>
     <row r="1151">
       <c r="A1151" s="1" t="n">
-        <v>46035.4374768518</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B1151" t="n">
         <v>1600</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31075,6 +31075,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1152">
+      <c r="A1152" s="1" t="n">
+        <v>46036.3333333333</v>
+      </c>
+      <c r="B1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1152" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1152" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="1" t="n">
+        <v>46037.3751273148</v>
+      </c>
+      <c r="B1153" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1153" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1153" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31103,7 +31103,7 @@
     </row>
     <row r="1153">
       <c r="A1153" s="1" t="n">
-        <v>46037.3751273148</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B1153" t="n">
         <v>200</v>
@@ -31124,6 +31124,32 @@
         <v>139</v>
       </c>
       <c r="H1153" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="1" t="n">
+        <v>46038.6409027778</v>
+      </c>
+      <c r="B1154" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1154" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31129,7 +31129,7 @@
     </row>
     <row r="1154">
       <c r="A1154" s="1" t="n">
-        <v>46038.6409027778</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B1154" t="n">
         <v>2000</v>
@@ -31150,6 +31150,32 @@
         <v>139</v>
       </c>
       <c r="H1154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="1" t="n">
+        <v>46041.5378703704</v>
+      </c>
+      <c r="B1155" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1155" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31155,7 +31155,7 @@
     </row>
     <row r="1155">
       <c r="A1155" s="1" t="n">
-        <v>46041.5378703704</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B1155" t="n">
         <v>600</v>
@@ -31176,6 +31176,32 @@
         <v>59</v>
       </c>
       <c r="H1155" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="1" t="n">
+        <v>46042.5403125</v>
+      </c>
+      <c r="B1156" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1156" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31181,7 +31181,7 @@
     </row>
     <row r="1156">
       <c r="A1156" s="1" t="n">
-        <v>46042.5403125</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B1156" t="n">
         <v>800</v>
@@ -31202,6 +31202,32 @@
         <v>139</v>
       </c>
       <c r="H1156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="1" t="n">
+        <v>46043.5500462963</v>
+      </c>
+      <c r="B1157" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1157" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1157" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31207,7 +31207,7 @@
     </row>
     <row r="1157">
       <c r="A1157" s="1" t="n">
-        <v>46043.5500462963</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B1157" t="n">
         <v>4400</v>
@@ -31228,6 +31228,32 @@
         <v>139</v>
       </c>
       <c r="H1157" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="1" t="n">
+        <v>46044.4106828704</v>
+      </c>
+      <c r="B1158" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1158" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1158" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31233,7 +31233,7 @@
     </row>
     <row r="1158">
       <c r="A1158" s="1" t="n">
-        <v>46044.4106828704</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B1158" t="n">
         <v>1200</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31257,6 +31257,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1159">
+      <c r="A1159" s="1" t="n">
+        <v>46045.3333333333</v>
+      </c>
+      <c r="B1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1159" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="1" t="n">
+        <v>46048.6475694444</v>
+      </c>
+      <c r="B1160" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1160" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31285,7 +31285,7 @@
     </row>
     <row r="1160">
       <c r="A1160" s="1" t="n">
-        <v>46048.6475694444</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B1160" t="n">
         <v>2600</v>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31309,6 +31309,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1161">
+      <c r="A1161" s="1" t="n">
+        <v>46049.3333333333</v>
+      </c>
+      <c r="B1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1161" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SPN.MI.xlsx
+++ b/data/SPN.MI.xlsx
@@ -31335,6 +31335,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" s="1" t="n">
+        <v>46050.3333333333</v>
+      </c>
+      <c r="B1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="G1162" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
